--- a/mockup_status.xlsx
+++ b/mockup_status.xlsx
@@ -421,8 +421,8 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="93.86214285714286" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="53.43357142857143" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
@@ -455,12 +455,12 @@
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\Admin\Downloads\Auto_download_mockup\Image_src\I've appeared that' enough\IATE-Dog</t>
+          <t>C:\Users\Admin\Downloads\Auto_download_mockup\Image_src\I've appeared that' enough\IATE-Rab</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>{"Item_Name": "Funny Pug T-Shirt Graphic Tee", "bullets": ["COMFORTABLE FIT: Made from high-quality, soft materials for a comfortable fit.", "FUNNY DESIGN: A humorous pug on a treadmill with a funny phrase.", "DURABLE: Long-lasting print and high-quality fabric.", "GREAT GIFT: Perfect for dog lovers and fitness enthusiasts.", "UNIQUE STYLE: Stand out with this one-of-a-kind design."], "description": "Get ready to turn heads with this hilarious pug t-shirt! Featuring a funny graphic of a pug on a treadmill with the phrase 'I've appeared. That's enough.', this tee is perfect for dog lovers and fitness enthusiasts alike. Made from high-quality, soft materials, this shirt is not only stylish but also comfortable to wear. The durable print and fabric ensure that it will remain a favorite for a long time. Whether you're looking for a unique gift or a fun addition to your own wardrobe, this pug t-shirt is sure to bring a smile to everyone's face.", "keywords": ["pug t shirt", "funny dog tee", "fitness humor", "pet lovers shirt", "treadmill pug", "comfy tees", "unique gifts", "dog graphic tee", "humorous apparel", "pug lover shirt"], "subject_character": "Pug", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820697/pod/IATE-Dog/IATE-Dog-b-1_ebhn0m.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820698/pod/IATE-Dog/IATE-Dog-b-2_fahwdd.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820699/pod/IATE-Dog/IATE-Dog-b-3_hmbpod.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820701/pod/IATE-Dog/IATE-Dog-b-4_xl0jr9.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820702/pod/IATE-Dog/IATE-Dog-b-5_n79yfm.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820704/pod/IATE-Dog/IATE-Dog-b-6_l88l4y.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820706/pod/IATE-Dog/IATE-Dog-b-7_qqlno4.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820708/pod/IATE-Dog/IATE-Dog-b-8_uqwx94.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820709/pod/IATE-Dog/IATE-Dog-w-1_ntcb0o.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820710/pod/IATE-Dog/IATE-Dog-w-2_j08b6d.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820712/pod/IATE-Dog/IATE-Dog-w-3_rxe3il.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820713/pod/IATE-Dog/IATE-Dog-w-4_kftrgj.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820715/pod/IATE-Dog/IATE-Dog-w-5_df342j.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820717/pod/IATE-Dog/IATE-Dog-w-6_iuhegw.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820719/pod/IATE-Dog/IATE-Dog-w-7_o3mywc.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820725/pod/IATE-Dog/IATE-Dog-w-8_dhk4p9.png"]}</t>
+          <t>{"Item_Name": "Funny Rabbit T-Shirt Graphic Workout Bunny Exercise Tee", "bullets": ["PREMIUM COMFORT: Soft and breathable fabric for all-day wear", "UNIQUE DESIGN: Adorable cartoon rabbit graphic on a black tee", "FUNNY QUOTE: 'I've appeared. That's enough.' adds humor to your outfit", "GREAT FOR GYM: Perfect for fitness enthusiasts with a sense of humor", "VERSATILE STYLE: Wear it to the gym, for a casual outing, or lounging around"], "description": "Get fit and look great with our Funny Rabbit T-Shirt! This graphic tee features a cartoon bunny on a stationary bike, wearing a hoodie and sunglasses, with the humorous phrase 'I've appeared. That's enough.' Printed on a high-quality black t-shirt, this tee is perfect for anyone who loves a good laugh and a comfortable workout outfit. Made from soft, breathable fabric, you'll want to wear it again and again.", "keywords": ["funny rabbit t shirt", "graphic workout tee", "cartoon bunny shirt", "gym humor", "fitness apparel", "humorous t shirts", "exercise tee", "workout clothing", "funny fitness gear", "rabbit graphic tee"], "subject_character": "Rabbit", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277609/pod/IATE-Rab/IATE-Rab-b-1_d3iqu0.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277610/pod/IATE-Rab/IATE-Rab-b-2_lqv2oh.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277612/pod/IATE-Rab/IATE-Rab-b-3_limgca.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277613/pod/IATE-Rab/IATE-Rab-b-4_be1n7l.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277614/pod/IATE-Rab/IATE-Rab-b-5_wku7pk.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277615/pod/IATE-Rab/IATE-Rab-b-6_npbsma.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277618/pod/IATE-Rab/IATE-Rab-b-7_tsiaic.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277620/pod/IATE-Rab/IATE-Rab-b-8_laat2h.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277621/pod/IATE-Rab/IATE-Rab-w-1_w988pp.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277622/pod/IATE-Rab/IATE-Rab-w-2_uwwqt1.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277623/pod/IATE-Rab/IATE-Rab-w-3_av4d7s.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277624/pod/IATE-Rab/IATE-Rab-w-4_ylmnvu.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277625/pod/IATE-Rab/IATE-Rab-w-5_dicjlb.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277627/pod/IATE-Rab/IATE-Rab-w-6_fjkhqt.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277629/pod/IATE-Rab/IATE-Rab-w-7_de4y2n.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277631/pod/IATE-Rab/IATE-Rab-w-8_uucqqf.png"]}</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -471,20 +471,6 @@
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>done</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\Admin\Downloads\Auto_download_mockup\Image_src\I've appeared that' enough\IATE-Cat</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>created</t>
         </is>
       </c>
     </row>

--- a/mockup_status.xlsx
+++ b/mockup_status.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="93.86214285714286" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -458,9 +458,9 @@
           <t>C:\Users\Admin\Downloads\Auto_download_mockup\Image_src\I've appeared that' enough\IATE-Rab</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>{"Item_Name": "Funny Rabbit T-Shirt Graphic Workout Bunny Exercise Tee", "bullets": ["PREMIUM COMFORT: Soft and breathable fabric for all-day wear", "UNIQUE DESIGN: Adorable cartoon rabbit graphic on a black tee", "FUNNY QUOTE: 'I've appeared. That's enough.' adds humor to your outfit", "GREAT FOR GYM: Perfect for fitness enthusiasts with a sense of humor", "VERSATILE STYLE: Wear it to the gym, for a casual outing, or lounging around"], "description": "Get fit and look great with our Funny Rabbit T-Shirt! This graphic tee features a cartoon bunny on a stationary bike, wearing a hoodie and sunglasses, with the humorous phrase 'I've appeared. That's enough.' Printed on a high-quality black t-shirt, this tee is perfect for anyone who loves a good laugh and a comfortable workout outfit. Made from soft, breathable fabric, you'll want to wear it again and again.", "keywords": ["funny rabbit t shirt", "graphic workout tee", "cartoon bunny shirt", "gym humor", "fitness apparel", "humorous t shirts", "exercise tee", "workout clothing", "funny fitness gear", "rabbit graphic tee"], "subject_character": "Rabbit", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277609/pod/IATE-Rab/IATE-Rab-b-1_d3iqu0.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277610/pod/IATE-Rab/IATE-Rab-b-2_lqv2oh.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277612/pod/IATE-Rab/IATE-Rab-b-3_limgca.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277613/pod/IATE-Rab/IATE-Rab-b-4_be1n7l.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277614/pod/IATE-Rab/IATE-Rab-b-5_wku7pk.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277615/pod/IATE-Rab/IATE-Rab-b-6_npbsma.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277618/pod/IATE-Rab/IATE-Rab-b-7_tsiaic.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277620/pod/IATE-Rab/IATE-Rab-b-8_laat2h.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277621/pod/IATE-Rab/IATE-Rab-w-1_w988pp.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277622/pod/IATE-Rab/IATE-Rab-w-2_uwwqt1.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277623/pod/IATE-Rab/IATE-Rab-w-3_av4d7s.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277624/pod/IATE-Rab/IATE-Rab-w-4_ylmnvu.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277625/pod/IATE-Rab/IATE-Rab-w-5_dicjlb.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277627/pod/IATE-Rab/IATE-Rab-w-6_fjkhqt.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277629/pod/IATE-Rab/IATE-Rab-w-7_de4y2n.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775277631/pod/IATE-Rab/IATE-Rab-w-8_uucqqf.png"]}</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>{"Item_Name": "Funny Rabbit T-Shirt Graphic Workout Bunny Cotton Tee", "bullets": ["PREMIUM COMFORT: Soft and breathable cotton for all-day wear", "UNIQUE GRAPHIC: Adorable rabbit design with a humorous workout twist", "DURABLE QUALITY: Long-lasting print and comfortable fit", "FUN FOR ALL: Perfect for fitness enthusiasts and animal lovers alike", "GREAT GIFT: Ideal for friends and family who love to laugh and workout"], "description": "Get ready to hop into fitness with our Funny Rabbit T-Shirt! This graphic tee features an adorable rabbit in a humorous workout setting, complete with a stationary bike, dumbbells, and a coffee cup. Made from soft and breathable cotton, this tee is perfect for anyone who loves to laugh and stay active. The unique design and durable quality make it a great addition to any wardrobe. Whether you're hitting the gym or just lounging around, this funny rabbit shirt is sure to bring a smile to your face.", "keywords": ["funny rabbit t-shirt", "graphic workout tee", "cotton t-shirt", "humorous fitness shirt", "workout bunny tee", "funny animal shirt", "exercise rabbit t-shirt", "gym tee", "fitness apparel", "humorous gift", "t-shirt for fitness enthusiasts"], "subject_character": "Rabbit", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316093/pod/IATE-Rab/IATE-Rab-b-1_yurz3m.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316094/pod/IATE-Rab/IATE-Rab-b-2_e9kvp4.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316095/pod/IATE-Rab/IATE-Rab-b-3_owscv8.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316096/pod/IATE-Rab/IATE-Rab-b-4_giwabx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316097/pod/IATE-Rab/IATE-Rab-b-5_xrk9ot.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316099/pod/IATE-Rab/IATE-Rab-b-6_vzb3j3.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316101/pod/IATE-Rab/IATE-Rab-b-7_luqe0d.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316103/pod/IATE-Rab/IATE-Rab-b-8_tbsps9.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316106/pod/IATE-Rab/IATE-Rab-w-1_k1hu5f.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316107/pod/IATE-Rab/IATE-Rab-w-2_kcngmy.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316108/pod/IATE-Rab/IATE-Rab-w-3_hzsmgx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316109/pod/IATE-Rab/IATE-Rab-w-4_pcbueb.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316110/pod/IATE-Rab/IATE-Rab-w-5_tbhfre.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316112/pod/IATE-Rab/IATE-Rab-w-6_gvigsf.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316114/pod/IATE-Rab/IATE-Rab-w-7_caxpyx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316116/pod/IATE-Rab/IATE-Rab-w-8_miktxp.png"]}</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -471,6 +471,16 @@
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>created</t>
         </is>
       </c>
     </row>
